--- a/demo_sap.xlsx
+++ b/demo_sap.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5970f73ce23ace4e/IMS_AI_DEMO/Work_experince/Work_Experience/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5970f73ce23ace4e/IMS_AI_DEMO/Work_Experience/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_50F971BDD3105102A77B2411595ED87656CDFF44" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0836BC2-9C5A-42E1-8FAE-549823A189A9}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_50F971BDD3105102A77B2411595ED87656CDFF44" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CE71C4D-00BF-404A-B2E0-A9D7ABD58F0A}"/>
   <bookViews>
-    <workbookView xWindow="6400" yWindow="2060" windowWidth="19200" windowHeight="12170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="144">
   <si>
     <t>OrderNumber</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Left at front door</t>
   </si>
   <si>
-    <t>+447911000002</t>
-  </si>
-  <si>
     <t>2025-08-16</t>
   </si>
   <si>
@@ -254,9 +251,6 @@
   </si>
   <si>
     <t>+447911000034</t>
-  </si>
-  <si>
-    <t>+447911000035</t>
   </si>
   <si>
     <t>+447911000036</t>
@@ -820,9 +814,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="18.36328125" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
     <col min="7" max="7" width="21" customWidth="1"/>
   </cols>
   <sheetData>
@@ -897,275 +893,275 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4" t="s">
         <v>18</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
         <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
         <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>27</v>
       </c>
       <c r="F7">
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
         <v>31</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
-      <c r="G8" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s">
         <v>36</v>
       </c>
-      <c r="E10" t="s">
-        <v>37</v>
-      </c>
       <c r="F10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B12" t="s">
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
         <v>21</v>
       </c>
-      <c r="D13" t="s">
-        <v>42</v>
-      </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="F13">
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B14" t="s">
         <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G14" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
@@ -1173,45 +1169,45 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B17" t="s">
         <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G17" t="s">
         <v>15</v>
@@ -1219,122 +1215,122 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="E18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B19" t="s">
         <v>53</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E19" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G19" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B20" t="s">
         <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E20" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G20" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" t="s">
         <v>55</v>
       </c>
-      <c r="C21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21" t="s">
-        <v>56</v>
-      </c>
       <c r="F21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B22" t="s">
         <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B23" t="s">
         <v>58</v>
@@ -1343,128 +1339,128 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E23" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B25" t="s">
         <v>61</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D27" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="E27" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B28" t="s">
         <v>66</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="F28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G28" t="s">
         <v>11</v>
@@ -1472,206 +1468,206 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D29" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="E29" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B30" t="s">
         <v>69</v>
       </c>
       <c r="C30" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="E30" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G30" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B31" t="s">
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D31" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E31" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B32" t="s">
         <v>71</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D32" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E32" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G32" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C33" t="s">
         <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E33" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="F33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G33" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B34" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" t="s">
         <v>74</v>
       </c>
-      <c r="C34" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" t="s">
-        <v>75</v>
-      </c>
       <c r="E34" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="F34">
         <v>2</v>
       </c>
       <c r="G34" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B35" t="s">
         <v>76</v>
       </c>
       <c r="C35" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="E35" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F35">
         <v>2</v>
       </c>
       <c r="G35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>1034</v>
-      </c>
-      <c r="B36" t="s">
-        <v>77</v>
+        <v>1035</v>
+      </c>
+      <c r="B36">
+        <v>447911000035</v>
       </c>
       <c r="C36" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C37" t="s">
         <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="E37" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37" t="s">
         <v>11</v>
@@ -1679,114 +1675,114 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B38" t="s">
+        <v>78</v>
+      </c>
+      <c r="C38" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" t="s">
         <v>79</v>
       </c>
-      <c r="C38" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" t="s">
-        <v>75</v>
-      </c>
       <c r="E38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F38">
         <v>2</v>
       </c>
       <c r="G38" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B39" t="s">
         <v>80</v>
       </c>
       <c r="C39" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D39" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E39" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B40" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D40" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E40" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="F40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G40" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B41" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D41" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="E41" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G41" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B42" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C42" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E42" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G42" t="s">
         <v>11</v>
@@ -1794,214 +1790,214 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C43" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D43" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E43" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C44" t="s">
         <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="E44" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C45" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D45" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="E45" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G45" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B46" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D46" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="E46" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46">
+        <v>5</v>
+      </c>
+      <c r="G46" t="s">
         <v>43</v>
-      </c>
-      <c r="F46">
-        <v>2</v>
-      </c>
-      <c r="G46" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B47" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D47" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E47" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F47">
         <v>5</v>
       </c>
       <c r="G47" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B48" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C48" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D48" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E48" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F48">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B49" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C49" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" t="s">
         <v>25</v>
       </c>
-      <c r="D49" t="s">
-        <v>36</v>
-      </c>
       <c r="E49" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C50" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D50" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" t="s">
         <v>26</v>
       </c>
-      <c r="E50" t="s">
-        <v>43</v>
-      </c>
       <c r="F50">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G50" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B51" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" t="s">
         <v>93</v>
       </c>
-      <c r="C51" t="s">
-        <v>21</v>
-      </c>
-      <c r="D51" t="s">
-        <v>17</v>
-      </c>
       <c r="E51" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B52" t="s">
         <v>94</v>
@@ -2010,749 +2006,749 @@
         <v>8</v>
       </c>
       <c r="D52" t="s">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="E52" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G52" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B53" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C53" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D53" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E53" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F53">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G53" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B54" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C54" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="E54" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F54">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B55" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C55" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D55" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B56" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C56" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D56" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E56" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G56" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B57" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C57" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D57" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E57" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B58" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C58" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" t="s">
         <v>21</v>
       </c>
-      <c r="D58" t="s">
-        <v>75</v>
-      </c>
       <c r="E58" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B59" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C59" t="s">
         <v>8</v>
       </c>
       <c r="D59" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="E59" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G59" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B60" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C60" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D60" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="E60" t="s">
+        <v>17</v>
+      </c>
+      <c r="F60">
+        <v>5</v>
+      </c>
+      <c r="G60" t="s">
         <v>18</v>
-      </c>
-      <c r="F60">
-        <v>3</v>
-      </c>
-      <c r="G60" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B61" t="s">
+        <v>103</v>
+      </c>
+      <c r="C61" t="s">
+        <v>24</v>
+      </c>
+      <c r="D61" t="s">
         <v>104</v>
       </c>
-      <c r="C61" t="s">
-        <v>21</v>
-      </c>
-      <c r="D61" t="s">
-        <v>65</v>
-      </c>
       <c r="E61" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F61">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B62" t="s">
         <v>105</v>
       </c>
       <c r="C62" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D62" t="s">
-        <v>106</v>
+        <v>64</v>
       </c>
       <c r="E62" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G62" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B63" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C63" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D63" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="E63" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="F63">
         <v>5</v>
       </c>
       <c r="G63" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B64" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D64" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E64" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="F64">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G64" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B65" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C65" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D65" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="E65" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G65" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B66" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C66" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="E66" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F66">
         <v>3</v>
       </c>
       <c r="G66" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B67" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C67" t="s">
         <v>13</v>
       </c>
       <c r="D67" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="E67" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F67">
         <v>3</v>
       </c>
       <c r="G67" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B68" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C68" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D68" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="E68" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F68">
         <v>3</v>
       </c>
       <c r="G68" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B69" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C69" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D69" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="E69" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F69">
         <v>3</v>
       </c>
       <c r="G69" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B70" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C70" t="s">
         <v>8</v>
       </c>
       <c r="D70" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="E70" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G70" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B71" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C71" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D71" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E71" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F71">
         <v>2</v>
       </c>
       <c r="G71" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B72" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C72" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D72" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E72" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F72">
         <v>2</v>
       </c>
       <c r="G72" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B73" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C73" t="s">
         <v>8</v>
       </c>
       <c r="D73" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="E73" t="s">
         <v>10</v>
       </c>
       <c r="F73">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G73" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B74" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C74" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D74" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="E74" t="s">
         <v>10</v>
       </c>
       <c r="F74">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G74" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B75" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C75" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" t="s">
         <v>21</v>
       </c>
-      <c r="D75" t="s">
-        <v>73</v>
-      </c>
       <c r="E75" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="F75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G75" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B76" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C76" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D76" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E76" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="F76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G76" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B77" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C77" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D77" t="s">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="E77" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G77" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B78" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C78" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D78" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E78" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G78" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B79" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C79" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D79" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E79" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F79">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G79" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B80" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C80" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D80" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="E80" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F80">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G80" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B81" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C81" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D81" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="E81" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F81">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G81" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B82" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C82" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D82" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="E82" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B83" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C83" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D83" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="E83" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G83" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B84" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C84" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D84" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="E84" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F84">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G84" t="s">
         <v>11</v>
@@ -2760,91 +2756,91 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B85" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C85" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D85" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="E85" t="s">
         <v>10</v>
       </c>
       <c r="F85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G85" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B86" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C86" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D86" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="E86" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G86" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B87" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C87" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D87" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="E87" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F87">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G87" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B88" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C88" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D88" t="s">
         <v>14</v>
       </c>
       <c r="E88" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="F88">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G88" t="s">
         <v>11</v>
@@ -2852,301 +2848,278 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B89" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C89" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D89" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E89" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F89">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G89" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B90" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C90" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" t="s">
         <v>21</v>
       </c>
-      <c r="D90" t="s">
-        <v>31</v>
-      </c>
       <c r="E90" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F90">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G90" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B91" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C91" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D91" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="E91" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F91">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B92" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C92" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D92" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="E92" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G92" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B93" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C93" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D93" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="E93" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F93">
         <v>4</v>
       </c>
       <c r="G93" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B94" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C94" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D94" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="E94" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F94">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G94" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B95" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C95" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D95" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E95" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F95">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G95" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B96" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C96" t="s">
         <v>13</v>
       </c>
       <c r="D96" t="s">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="E96" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="F96">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G96" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B97" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C97" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D97" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="E97" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="F97">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G97" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B98" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C98" t="s">
+        <v>24</v>
+      </c>
+      <c r="D98" t="s">
         <v>25</v>
       </c>
-      <c r="D98" t="s">
-        <v>39</v>
-      </c>
       <c r="E98" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F98">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G98" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B99" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C99" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D99" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="E99" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F99">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G99" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B100" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C100" t="s">
+        <v>13</v>
+      </c>
+      <c r="D100" t="s">
         <v>25</v>
       </c>
-      <c r="D100" t="s">
-        <v>9</v>
-      </c>
       <c r="E100" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F100">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G100" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A101">
-        <v>1099</v>
-      </c>
-      <c r="B101" t="s">
-        <v>145</v>
-      </c>
-      <c r="C101" t="s">
-        <v>13</v>
-      </c>
-      <c r="D101" t="s">
-        <v>26</v>
-      </c>
-      <c r="E101" t="s">
-        <v>23</v>
-      </c>
-      <c r="F101">
-        <v>1</v>
-      </c>
-      <c r="G101" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/demo_sap.xlsx
+++ b/demo_sap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5970f73ce23ace4e/IMS_AI_DEMO/Work_Experience/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_50F971BDD3105102A77B2411595ED87656CDFF44" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CE71C4D-00BF-404A-B2E0-A9D7ABD58F0A}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_50F971BDD3105102A77B2411595ED87656CDFF44" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38BEE428-9111-4552-B21B-DA78A6D12984}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="143">
   <si>
     <t>OrderNumber</t>
   </si>
@@ -407,9 +407,6 @@
   </si>
   <si>
     <t>+447911000084</t>
-  </si>
-  <si>
-    <t>+447911000085</t>
   </si>
   <si>
     <t>+447911000086</t>
@@ -472,12 +469,18 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -507,11 +510,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -527,6 +531,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -819,6 +827,7 @@
   <cols>
     <col min="1" max="1" width="18.36328125" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="5" max="5" width="20.81640625" customWidth="1"/>
     <col min="7" max="7" width="21" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1102,7 +1111,7 @@
       <c r="A13">
         <v>1012</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C13" t="s">
@@ -1240,7 +1249,7 @@
       <c r="A19">
         <v>1018</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C19" t="s">
@@ -1562,7 +1571,7 @@
       <c r="A33">
         <v>1032</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C33" t="s">
@@ -2712,7 +2721,7 @@
       <c r="A83">
         <v>1082</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C83" t="s">
@@ -2781,8 +2790,8 @@
       <c r="A86">
         <v>1085</v>
       </c>
-      <c r="B86" t="s">
-        <v>129</v>
+      <c r="B86">
+        <v>447911000085</v>
       </c>
       <c r="C86" t="s">
         <v>8</v>
@@ -2805,7 +2814,7 @@
         <v>1086</v>
       </c>
       <c r="B87" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C87" t="s">
         <v>20</v>
@@ -2828,7 +2837,7 @@
         <v>1087</v>
       </c>
       <c r="B88" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C88" t="s">
         <v>24</v>
@@ -2851,7 +2860,7 @@
         <v>1088</v>
       </c>
       <c r="B89" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C89" t="s">
         <v>20</v>
@@ -2874,7 +2883,7 @@
         <v>1089</v>
       </c>
       <c r="B90" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C90" t="s">
         <v>8</v>
@@ -2897,7 +2906,7 @@
         <v>1090</v>
       </c>
       <c r="B91" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C91" t="s">
         <v>24</v>
@@ -2920,7 +2929,7 @@
         <v>1091</v>
       </c>
       <c r="B92" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C92" t="s">
         <v>20</v>
@@ -2943,7 +2952,7 @@
         <v>1092</v>
       </c>
       <c r="B93" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C93" t="s">
         <v>24</v>
@@ -2966,7 +2975,7 @@
         <v>1093</v>
       </c>
       <c r="B94" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C94" t="s">
         <v>24</v>
@@ -2989,7 +2998,7 @@
         <v>1094</v>
       </c>
       <c r="B95" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C95" t="s">
         <v>13</v>
@@ -3012,7 +3021,7 @@
         <v>1095</v>
       </c>
       <c r="B96" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C96" t="s">
         <v>13</v>
@@ -3035,7 +3044,7 @@
         <v>1096</v>
       </c>
       <c r="B97" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C97" t="s">
         <v>24</v>
@@ -3058,7 +3067,7 @@
         <v>1097</v>
       </c>
       <c r="B98" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C98" t="s">
         <v>24</v>
@@ -3081,7 +3090,7 @@
         <v>1098</v>
       </c>
       <c r="B99" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C99" t="s">
         <v>24</v>
@@ -3104,7 +3113,7 @@
         <v>1099</v>
       </c>
       <c r="B100" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C100" t="s">
         <v>13</v>
